--- a/etf_holdings/2026-10-02_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.21%2510</t>
+          <t>-0.4%2500</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.26%870,000</t>
+          <t>9.28%870,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.26%</t>
+          <t>9.28%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.22%4980</t>
+          <t>+7.41%1305</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+7.41%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4980</v>
+        <v>1305</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.96%282,000</t>
+          <t>6.40%1,150,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.96%</t>
+          <t>6.40%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>282000</v>
+        <v>1150000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+3.4%1215</t>
+          <t>-0.6%4950</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1215</v>
+        <v>4950</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.93%1,150,000</t>
+          <t>5.95%282,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.93%</t>
+          <t>5.95%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1150000</v>
+        <v>282000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.18%3510</t>
+          <t>-1.99%3440</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3510</v>
+        <v>3440</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.85%393,000</t>
+          <t>5.77%393,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>5.77%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.81%4975</t>
+          <t>+4.22%5185</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4975</v>
+        <v>5185</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.98%236,000</t>
+          <t>5.22%236,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.98%</t>
+          <t>5.22%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.74%7900</t>
+          <t>0%7900</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.79%143,000</t>
+          <t>4.82%143,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.79%</t>
+          <t>4.82%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,34 +870,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.96%2110</t>
+          <t>+0.99%1535</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2110</v>
+        <v>1535</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.75%418,644</t>
+          <t>3.90%565,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.90%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>418644</v>
+        <v>565000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.99%1535</t>
+          <t>-1.18%2085</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1535</v>
+        <v>2085</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.68%565,000</t>
+          <t>3.72%418,644</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>565000</v>
+        <v>418644</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.1%6875</t>
+          <t>-1.09%6800</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6875</v>
+        <v>6800</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.56%122,000</t>
+          <t>3.54%122,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.54%2555</t>
+          <t>-0.59%2540</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2555</v>
+        <v>2540</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.97%1420</t>
+          <t>+2.82%1460</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.97%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1420</v>
+        <v>1460</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.05%506,000</t>
+          <t>3.15%506,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1%710</t>
+          <t>+0.42%713</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.01%998,000</t>
+          <t>3.04%998,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.04%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.79%1905</t>
+          <t>-1.05%1885</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.74%339,000</t>
+          <t>2.73%339,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,34 +1297,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.82%11835</t>
+          <t>-1.85%5030</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>11835</v>
+        <v>5030</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.61%52,000</t>
+          <t>2.72%120,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>52000</v>
+        <v>120000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:44</t>
+          <t>2026-10-02 19:06:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.85%5030</t>
+          <t>+2.62%12145</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5030</v>
+        <v>12145</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.56%120,000</t>
+          <t>2.69%52,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>120000</v>
+        <v>52000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+9.85%602</t>
+          <t>+3.99%626</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+3.99%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.40%939,000</t>
+          <t>2.51%939,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.51%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.49%1565</t>
+          <t>+3.42%1965</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1565</v>
+        <v>1965</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.15%324,000</t>
+          <t>2.11%252,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>324000</v>
+        <v>252000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+7.04%1900</t>
+          <t>-3.51%1510</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+7.04%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1900</v>
+        <v>1510</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.03%252,000</t>
+          <t>2.09%324,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>252000</v>
+        <v>324000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.85%22,900</t>
+          <t>1.84%22,900</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.79%284.5</t>
+          <t>-2.67%1275</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>284.5</v>
+        <v>1275</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.47%1,216,000</t>
+          <t>1.54%267,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1216000</v>
+        <v>267000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+4.37%6205</t>
+          <t>+1.37%6290</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+4.37%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6205</v>
+        <v>6290</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.45%55,000</t>
+          <t>1.48%55,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-2.67%1275</t>
+          <t>-1.3%2660</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1275</v>
+        <v>2660</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.44%267,000</t>
+          <t>1.48%119,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>267000</v>
+        <v>119000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,34 +1846,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.3%2660</t>
+          <t>-1.05%281.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2660</v>
+        <v>281.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.34%119,000</t>
+          <t>1.46%1,216,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>119000</v>
+        <v>1216000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.27%100,000</t>
+          <t>1.31%100,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.65%2390</t>
+          <t>-3.35%2310</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2390</v>
+        <v>2310</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.19%117,000</t>
+          <t>1.15%117,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+3.84%1000</t>
+          <t>+1.5%1015</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+3.84%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.08%255,000</t>
+          <t>1.10%255,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0%519</t>
+          <t>+10%561</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>519</v>
+        <v>561</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.98%447,000</t>
+          <t>1.05%438,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>447000</v>
+        <v>438000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.58%2080</t>
+          <t>+5.29%2190</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2080</v>
+        <v>2190</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.97%110,000</t>
+          <t>1.03%110,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,34 +2212,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.59%510</t>
+          <t>+1.35%526</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.95%438,000</t>
+          <t>1.00%447,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>438000</v>
+        <v>447000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:46</t>
+          <t>2026-10-02 19:06:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.85%84,000</t>
+          <t>0.87%84,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.59%254</t>
+          <t>+2.36%260</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.79%729,000</t>
+          <t>0.81%729,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.18%547</t>
+          <t>-1.83%537</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-1.83%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.74%317,000</t>
+          <t>0.73%317,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+3.25%190.5</t>
+          <t>-2.1%186.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+3.25%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>190.5</v>
+        <v>186.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.74%921,000</t>
+          <t>0.73%921,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>2615萬海</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.82%3245</t>
+          <t>+0.44%113</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3245</v>
+        <v>113</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.69%50,000</t>
+          <t>0.68%1,415,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>50000</v>
+        <v>1415000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2615萬海</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.32%112.5</t>
+          <t>-1.82%3245</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>112.5</v>
+        <v>3245</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.68%1,415,000</t>
+          <t>0.68%50,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1415000</v>
+        <v>50000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+4.53%161.5</t>
+          <t>0%161.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.62%179,000</t>
+          <t>0.60%179,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-2.23%1095</t>
+          <t>+0.91%1105</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.55%119,000</t>
+          <t>0.56%119,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2451創見</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.17%289.5</t>
+          <t>+7.18%1000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+7.18%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>289.5</v>
+        <v>1000</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.32%264,000</t>
+          <t>0.35%81,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>264000</v>
+        <v>81000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,34 +2944,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5289宜鼎</t>
+          <t>2451創見</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0%1290</t>
+          <t>+0.17%290</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1290</v>
+        <v>290</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.32%58,294</t>
+          <t>0.33%264,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>58294</v>
+        <v>264000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>5289宜鼎</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.65%933</t>
+          <t>0%1290</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>933</v>
+        <v>1290</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.32%81,000</t>
+          <t>0.32%58,294</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>81000</v>
+        <v>58294</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-3.7%1170</t>
+          <t>-0.43%1165</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:47</t>
+          <t>2026-10-02 19:06:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.28%176,000</t>
+          <t>0.29%176,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:48</t>
+          <t>2026-10-02 19:06:22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.26%762</t>
+          <t>-1.05%754</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:48</t>
+          <t>2026-10-02 19:06:22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+2.16%567</t>
+          <t>+2.82%583</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.21%87,000</t>
+          <t>0.22%87,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:48</t>
+          <t>2026-10-02 19:06:22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.28%180</t>
+          <t>-0.56%179</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:48</t>
+          <t>2026-10-02 19:06:22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.25%1185</t>
+          <t>-0.42%1180</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:48</t>
+          <t>2026-10-02 19:06:22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.39%145.5</t>
+          <t>+0.34%146</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>145.5</v>
+        <v>146</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-02_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:18</t>
+          <t>2026-10-02 22:50:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:20</t>
+          <t>2026-10-02 22:50:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:21</t>
+          <t>2026-10-02 22:50:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:22</t>
+          <t>2026-10-02 22:50:53</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:22</t>
+          <t>2026-10-02 22:50:53</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:22</t>
+          <t>2026-10-02 22:50:53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:22</t>
+          <t>2026-10-02 22:50:53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:22</t>
+          <t>2026-10-02 22:50:53</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:49</t>
+          <t>2026-10-02 22:59:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:51</t>
+          <t>2026-10-02 22:59:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:52</t>
+          <t>2026-10-02 22:59:51</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:53</t>
+          <t>2026-10-02 23:00:02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:53</t>
+          <t>2026-10-02 23:00:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:53</t>
+          <t>2026-10-02 23:00:02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:53</t>
+          <t>2026-10-02 23:00:02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:53</t>
+          <t>2026-10-02 23:00:02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:28</t>
+          <t>2026-10-02 23:49:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:39</t>
+          <t>2026-10-02 23:49:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:51</t>
+          <t>2026-10-02 23:49:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:02</t>
+          <t>2026-10-02 23:49:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:02</t>
+          <t>2026-10-02 23:49:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:02</t>
+          <t>2026-10-02 23:49:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:02</t>
+          <t>2026-10-02 23:49:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:02</t>
+          <t>2026-10-02 23:49:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
